--- a/Matrice_Risques_Audit_DB.xlsx
+++ b/Matrice_Risques_Audit_DB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\Documents\cours Openclassrooms\Data Engineer\projet 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566BDD80-E37C-460D-946B-7474BFF4AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630DDC35-0258-4784-BC0F-53F9F681A843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="288" windowWidth="23232" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrice des Risques" sheetId="1" r:id="rId1"/>
@@ -278,9 +278,6 @@
     <t>Insertions tardives des ventes</t>
   </si>
   <si>
-    <t>Absence de contrôle de complétude</t>
-  </si>
-  <si>
     <t>Données sensibles dans la BI</t>
   </si>
   <si>
@@ -296,9 +293,6 @@
     <t>Données incomplètes dans Power BI</t>
   </si>
   <si>
-    <t>Publication de données non finalisées</t>
-  </si>
-  <si>
     <t>Risque sécurité / conformité</t>
   </si>
   <si>
@@ -315,9 +309,6 @@
   </si>
   <si>
     <t>Mettre en place une clôture journalière des ventes</t>
-  </si>
-  <si>
-    <t>Mettre en place des contrôles de complétude avant publication BI</t>
   </si>
   <si>
     <t>Restreindre les données personnelles dans la couche BI</t>
@@ -331,6 +322,15 @@
   </si>
   <si>
     <t>Séparer la date des ventes et la date d'insertion</t>
+  </si>
+  <si>
+    <t>Absence de supervision de la base de données</t>
+  </si>
+  <si>
+    <t>Origine des anomalies non identifiable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mettre en place une supervision technique </t>
   </si>
 </sst>
 </file>
@@ -555,21 +555,6 @@
   </cellStyleXfs>
   <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -579,24 +564,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -623,15 +590,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -677,25 +635,67 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1080,191 +1080,191 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="2" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
     </row>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
     </row>
     <row r="6" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
     </row>
     <row r="7" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
     </row>
     <row r="8" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
     </row>
     <row r="9" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
     </row>
     <row r="11" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
     </row>
     <row r="12" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="10"/>
-      <c r="C12" s="19" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
     </row>
     <row r="19" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
     </row>
     <row r="20" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="B20" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
     </row>
     <row r="21" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
     </row>
     <row r="22" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1281,21 +1281,21 @@
     <row r="34" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1324,237 +1324,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
     </row>
     <row r="2" spans="2:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
     </row>
     <row r="3" spans="2:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="17" t="str">
+        <f t="shared" ref="H4:H9" si="0">IF(OR(F4="",G4=""),"",IF(AND(F4="Élevée",G4="Élevé"),"CRITIQUE",IF(OR(AND(F4="Élevée",G4="Moyen"),AND(F4="Moyenne",G4="Élevé")),"ÉLEVÉ",IF(OR(AND(F4="Élevée",G4="Faible"),AND(F4="Moyenne",G4="Moyen"),AND(F4="Faible",G4="Élevé")),"MOYEN","FAIBLE"))))</f>
+        <v>CRITIQUE</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="2:12" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G5" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="31" t="str">
-        <f>IF(OR(F4="",G4=""),"",IF(AND(F4="Élevée",G4="Élevé"),"CRITIQUE",IF(OR(AND(F4="Élevée",G4="Moyen"),AND(F4="Moyenne",G4="Élevé")),"ÉLEVÉ",IF(OR(AND(F4="Élevée",G4="Faible"),AND(F4="Moyenne",G4="Moyen"),AND(F4="Faible",G4="Élevé")),"MOYEN","FAIBLE"))))</f>
+      <c r="H5" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>CRITIQUE</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="I5" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+    </row>
+    <row r="6" spans="2:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>CRITIQUE</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+    </row>
+    <row r="7" spans="2:12" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>ÉLEVÉ</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+    </row>
+    <row r="8" spans="2:12" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="B8" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>ÉLEVÉ</v>
+      </c>
+      <c r="I8" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-    </row>
-    <row r="5" spans="2:12" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="31" t="str">
-        <f>IF(OR(F5="",G5=""),"",IF(AND(F5="Élevée",G5="Élevé"),"CRITIQUE",IF(OR(AND(F5="Élevée",G5="Moyen"),AND(F5="Moyenne",G5="Élevé")),"ÉLEVÉ",IF(OR(AND(F5="Élevée",G5="Faible"),AND(F5="Moyenne",G5="Moyen"),AND(F5="Faible",G5="Élevé")),"MOYEN","FAIBLE"))))</f>
-        <v>CRITIQUE</v>
-      </c>
-      <c r="I5" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-    </row>
-    <row r="6" spans="2:12" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="29" t="s">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+    </row>
+    <row r="9" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="31" t="str">
-        <f>IF(OR(F6="",G6=""),"",IF(AND(F6="Élevée",G6="Élevé"),"CRITIQUE",IF(OR(AND(F6="Élevée",G6="Moyen"),AND(F6="Moyenne",G6="Élevé")),"ÉLEVÉ",IF(OR(AND(F6="Élevée",G6="Faible"),AND(F6="Moyenne",G6="Moyen"),AND(F6="Faible",G6="Élevé")),"MOYEN","FAIBLE"))))</f>
-        <v>ÉLEVÉ</v>
-      </c>
-      <c r="I6" s="49" t="s">
+      <c r="G9" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>MOYEN</v>
+      </c>
+      <c r="I9" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-    </row>
-    <row r="7" spans="2:12" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="31" t="str">
-        <f>IF(OR(F7="",G7=""),"",IF(AND(F7="Élevée",G7="Élevé"),"CRITIQUE",IF(OR(AND(F7="Élevée",G7="Moyen"),AND(F7="Moyenne",G7="Élevé")),"ÉLEVÉ",IF(OR(AND(F7="Élevée",G7="Faible"),AND(F7="Moyenne",G7="Moyen"),AND(F7="Faible",G7="Élevé")),"MOYEN","FAIBLE"))))</f>
-        <v>ÉLEVÉ</v>
-      </c>
-      <c r="I7" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-    </row>
-    <row r="8" spans="2:12" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="31" t="str">
-        <f>IF(OR(F8="",G8=""),"",IF(AND(F8="Élevée",G8="Élevé"),"CRITIQUE",IF(OR(AND(F8="Élevée",G8="Moyen"),AND(F8="Moyenne",G8="Élevé")),"ÉLEVÉ",IF(OR(AND(F8="Élevée",G8="Faible"),AND(F8="Moyenne",G8="Moyen"),AND(F8="Faible",G8="Élevé")),"MOYEN","FAIBLE"))))</f>
-        <v>ÉLEVÉ</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-    </row>
-    <row r="9" spans="2:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="31" t="str">
-        <f>IF(OR(F9="",G9=""),"",IF(AND(F9="Élevée",G9="Élevé"),"CRITIQUE",IF(OR(AND(F9="Élevée",G9="Moyen"),AND(F9="Moyenne",G9="Élevé")),"ÉLEVÉ",IF(OR(AND(F9="Élevée",G9="Faible"),AND(F9="Moyenne",G9="Moyen"),AND(F9="Faible",G9="Élevé")),"MOYEN","FAIBLE"))))</f>
-        <v>MOYEN</v>
-      </c>
-      <c r="I9" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1625,218 +1625,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="2" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
     </row>
     <row r="3" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="51">
         <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"CRITIQUE")</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="51"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="45">
+        <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"ÉLEVÉ")</f>
         <v>2</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="34"/>
-    </row>
-    <row r="6" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4">
-        <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"ÉLEVÉ")</f>
-        <v>3</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="36"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="48">
         <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"MOYEN")</f>
         <v>1</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="38"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="8" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="49">
         <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"FAIBLE")</f>
         <v>0</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="40"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="50">
         <f>COUNTA('Registre des Vulnérabilités'!H4:H86)</f>
         <v>6</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="42"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="28"/>
     </row>
     <row r="10" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="49">
         <f>COUNTIF('Registre des Vulnérabilités'!L4:L86,"Résolu")</f>
         <v>0</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="40"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="26"/>
     </row>
     <row r="11" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="48">
         <f>COUNTIF('Registre des Vulnérabilités'!L4:L86,"En cours")</f>
         <v>0</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="38"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="24"/>
     </row>
     <row r="12" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="45">
         <f>COUNTIF('Registre des Vulnérabilités'!L4:L86,"À traiter")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="36"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="22"/>
     </row>
     <row r="13" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
     </row>
     <row r="15" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46">
+      <c r="C15" s="46"/>
+      <c r="D15" s="47">
         <f>IFERROR(COUNTIF('Registre des Vulnérabilités'!L4:L86,"Résolu")/COUNTA('Registre des Vulnérabilités'!H4:H86),0)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="46"/>
+      <c r="E15" s="47"/>
     </row>
     <row r="16" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C18" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="47"/>
+      <c r="E18" s="44"/>
     </row>
     <row r="19" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="47"/>
+      <c r="E20" s="44"/>
     </row>
     <row r="21" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="47"/>
+      <c r="E22" s="44"/>
     </row>
     <row r="23" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1856,27 +1856,27 @@
     <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Matrice_Risques_Audit_DB.xlsx
+++ b/Matrice_Risques_Audit_DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\Documents\cours Openclassrooms\Data Engineer\projet 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630DDC35-0258-4784-BC0F-53F9F681A843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AADD88C-B0F3-4C4F-937A-3986C69E83D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,9 +308,6 @@
     <t>Élevée : exploitation public, accès facile</t>
   </si>
   <si>
-    <t>Mettre en place une clôture journalière des ventes</t>
-  </si>
-  <si>
     <t>Restreindre les données personnelles dans la couche BI</t>
   </si>
   <si>
@@ -331,6 +328,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mettre en place une supervision technique </t>
+  </si>
+  <si>
+    <t>Mettre en place un contrôle quotidien des ventes</t>
   </si>
 </sst>
 </file>
@@ -644,7 +644,25 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -656,47 +674,29 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1079,30 +1079,30 @@
     <col min="6" max="6" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+    <row r="1" spans="2:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
     </row>
     <row r="2" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
     </row>
     <row r="5" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
@@ -1146,12 +1146,12 @@
     </row>
     <row r="9" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
     </row>
     <row r="11" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="39" t="s">
@@ -1219,52 +1219,52 @@
     </row>
     <row r="16" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
     </row>
     <row r="18" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
     </row>
     <row r="19" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
     </row>
     <row r="20" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
     </row>
     <row r="21" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
     </row>
     <row r="22" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1281,21 +1281,21 @@
     <row r="34" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1324,34 +1324,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
     </row>
     <row r="2" spans="2:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
     </row>
     <row r="3" spans="2:12" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="13" t="s">
@@ -1410,7 +1410,7 @@
         <v>CRITIQUE</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
@@ -1438,7 +1438,7 @@
         <v>CRITIQUE</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
@@ -1449,11 +1449,11 @@
         <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>39</v>
@@ -1466,7 +1466,7 @@
         <v>CRITIQUE</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -1494,7 +1494,7 @@
         <v>ÉLEVÉ</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
@@ -1522,7 +1522,7 @@
         <v>ÉLEVÉ</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -1550,7 +1550,7 @@
         <v>MOYEN</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J9" s="18"/>
       <c r="K9" s="18"/>
@@ -1625,39 +1625,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
     </row>
     <row r="2" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
     </row>
     <row r="5" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="44">
         <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"CRITIQUE")</f>
         <v>3</v>
       </c>
-      <c r="D5" s="51"/>
+      <c r="D5" s="44"/>
       <c r="E5" s="20"/>
     </row>
     <row r="6" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1675,55 +1675,55 @@
       <c r="B7" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="46">
         <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"MOYEN")</f>
         <v>1</v>
       </c>
-      <c r="D7" s="48"/>
+      <c r="D7" s="46"/>
       <c r="E7" s="24"/>
     </row>
     <row r="8" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="47">
         <f>COUNTIF('Registre des Vulnérabilités'!H4:H86,"FAIBLE")</f>
         <v>0</v>
       </c>
-      <c r="D8" s="49"/>
+      <c r="D8" s="47"/>
       <c r="E8" s="26"/>
     </row>
     <row r="9" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="48">
         <f>COUNTA('Registre des Vulnérabilités'!H4:H86)</f>
         <v>6</v>
       </c>
-      <c r="D9" s="50"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="28"/>
     </row>
     <row r="10" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="47">
         <f>COUNTIF('Registre des Vulnérabilités'!L4:L86,"Résolu")</f>
         <v>0</v>
       </c>
-      <c r="D10" s="49"/>
+      <c r="D10" s="47"/>
       <c r="E10" s="26"/>
     </row>
     <row r="11" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="46">
         <f>COUNTIF('Registre des Vulnérabilités'!L4:L86,"En cours")</f>
         <v>0</v>
       </c>
-      <c r="D11" s="48"/>
+      <c r="D11" s="46"/>
       <c r="E11" s="24"/>
     </row>
     <row r="12" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1739,32 +1739,32 @@
     </row>
     <row r="13" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
     </row>
     <row r="15" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="47">
+      <c r="C15" s="49"/>
+      <c r="D15" s="50">
         <f>IFERROR(COUNTIF('Registre des Vulnérabilités'!L4:L86,"Résolu")/COUNTA('Registre des Vulnérabilités'!H4:H86),0)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="47"/>
+      <c r="E15" s="50"/>
     </row>
     <row r="16" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
     </row>
     <row r="18" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
@@ -1773,10 +1773,10 @@
       <c r="C18" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="44"/>
+      <c r="E18" s="51"/>
     </row>
     <row r="19" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
@@ -1797,10 +1797,10 @@
       <c r="C20" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="44"/>
+      <c r="E20" s="51"/>
     </row>
     <row r="21" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
@@ -1821,10 +1821,10 @@
       <c r="C22" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="44"/>
+      <c r="E22" s="51"/>
     </row>
     <row r="23" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
@@ -1856,27 +1856,27 @@
     <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B17:E17"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D22:E22"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
